--- a/outputs/etf_trend_strategy/threshold_0.9/backtests/window_15/return_r2/post_rank_positive_return_rsi_bias_filter/staggered_10d/rsi_10_gt_60__bias_15_gt_-0.02/close/close_backtest_metrics.xlsx
+++ b/outputs/etf_trend_strategy/threshold_0.9/backtests/window_15/return_r2/post_rank_positive_return_rsi_bias_filter/staggered_10d/rsi_10_gt_60__bias_15_gt_-0.02/close/close_backtest_metrics.xlsx
@@ -563,7 +563,7 @@
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>0.8997429295314963</v>
+        <v>0.873183748148457</v>
       </c>
     </row>
     <row r="6">
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>-0.1002570704685103</v>
+        <v>-0.1268162518515448</v>
       </c>
     </row>
     <row r="7">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>-0.01981815940386178</v>
+        <v>-0.02536709570922757</v>
       </c>
     </row>
     <row r="8">
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>-0.003037347611308583</v>
+        <v>-0.008681282264872192</v>
       </c>
     </row>
     <row r="10">
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>0.2962404831937085</v>
+        <v>0.2117159446777974</v>
       </c>
     </row>
     <row r="11">
@@ -653,7 +653,7 @@
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>0.03046660916426581</v>
+        <v>-0.08583093541888991</v>
       </c>
     </row>
     <row r="12">
@@ -668,7 +668,7 @@
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>0.0434181187273731</v>
+        <v>-0.1211279167784572</v>
       </c>
     </row>
     <row r="13">
@@ -683,7 +683,7 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>0.5836502349726209</v>
+        <v>0.4669390324302375</v>
       </c>
     </row>
     <row r="14">
@@ -699,7 +699,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>2021年09月-2025年06月</t>
+          <t>2021年09月-2024年09月</t>
         </is>
       </c>
     </row>
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-0.03395554086394131</v>
+        <v>-0.0543263551500538</v>
       </c>
     </row>
     <row r="16">
@@ -730,7 +730,7 @@
         </is>
       </c>
       <c r="C16" s="5" t="n">
-        <v>0.2481653901051475</v>
+        <v>0.1894605141887553</v>
       </c>
     </row>
     <row r="17">
@@ -745,7 +745,7 @@
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.09097709198016392</v>
+        <v>-0.02438426335311926</v>
       </c>
     </row>
     <row r="18">
@@ -760,7 +760,7 @@
         </is>
       </c>
       <c r="C18" s="5" t="n">
-        <v>0.4511943748989151</v>
+        <v>0.3505608488757579</v>
       </c>
     </row>
     <row r="19">
@@ -776,7 +776,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2021年09月-2025年07月</t>
+          <t>2021年09月-2025年10月</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
         </is>
       </c>
       <c r="C20" s="6" t="n">
-        <v>17.3993854881439</v>
+        <v>12.90460480486544</v>
       </c>
     </row>
     <row r="21">
@@ -807,7 +807,7 @@
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>0.06956825005781436</v>
+        <v>0.05159669429554793</v>
       </c>
     </row>
     <row r="22">
@@ -822,7 +822,7 @@
         </is>
       </c>
       <c r="C22" s="5" t="n">
-        <v>0.1686219682501081</v>
+        <v>0.1282175849289694</v>
       </c>
     </row>
     <row r="23">
@@ -837,7 +837,7 @@
         </is>
       </c>
       <c r="C23" s="7" t="n">
-        <v>2.656390977443609</v>
+        <v>3.208270676691729</v>
       </c>
     </row>
     <row r="24">
@@ -1034,7 +1034,7 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>0.01</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="10">
